--- a/data/trans_orig/IP07KS_C10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C10_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de poder prestar atención en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de poder prestar atención, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58563</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50086</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67497</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>69,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39448</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32201</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45835</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>58,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51345</t>
+          <t>33745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69134</t>
+          <t>48356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99033</t>
+          <t>100007</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>87404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109786</t>
+          <t>111361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34927</t>
+          <t>39362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>21944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39381</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58812</t>
+          <t>60931</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47967</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>72469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13050</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4267</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3853</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13041</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97622</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97622</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97622</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>98502</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>98502</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>98502</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>166427</t>
+          <t>169228</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>166427</t>
+          <t>169228</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>166427</t>
+          <t>169228</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80119</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67161</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99913</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>57845</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29975</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75561</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>60780</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66672</t>
+          <t>51221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102684</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>139196</t>
+          <t>140898</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102387</t>
+          <t>122356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165099</t>
+          <t>159570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71715</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>77534</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58366</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108932</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71472</t>
+          <t>57639</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54348</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86739</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>149006</t>
+          <t>129355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123499</t>
+          <t>111931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192626</t>
+          <t>147524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15677</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9618</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24405</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6014</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2536</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11014</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6055</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5690</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10718</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3617</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>138682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>120430</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>157011</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>97293</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61452</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>117701</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140937</t>
+          <t>102223</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121030</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>115935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>238229</t>
+          <t>240905</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196708</t>
+          <t>219774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>264467</t>
+          <t>264584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>103328</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>85591</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121521</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>105205</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>84149</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>144460</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121684</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>207819</t>
+          <t>190285</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>167962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256062</t>
+          <t>212585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23123</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15647</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>34059</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6820</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23583</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41381</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11730</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6629</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6241</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11452</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>269203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>271285</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>271285</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>271285</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>576</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>481757</t>
+          <t>466791</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
